--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_COTO CÓRDOBA CB.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_COTO CÓRDOBA CB.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>41.2408</v>
+        <v>36.6876</v>
       </c>
       <c r="E2" t="n">
-        <v>28.0428</v>
+        <v>24.649</v>
       </c>
       <c r="F2" t="n">
-        <v>13.198</v>
+        <v>12.0388</v>
       </c>
       <c r="G2" t="n">
-        <v>37.0134</v>
+        <v>19.5413</v>
       </c>
       <c r="H2" t="n">
-        <v>31.3374</v>
+        <v>18.5591</v>
       </c>
       <c r="I2" t="n">
-        <v>5.676</v>
+        <v>0.9820000000000009</v>
       </c>
       <c r="J2" t="n">
-        <v>42.9972</v>
+        <v>35.6537</v>
       </c>
       <c r="K2" t="n">
-        <v>33.2393</v>
+        <v>27.9971</v>
       </c>
       <c r="L2" t="n">
-        <v>9.758000000000001</v>
+        <v>7.6561</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.9835</v>
+        <v>-16.1123</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.9018</v>
+        <v>-9.438700000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.082</v>
+        <v>-6.6742</v>
       </c>
       <c r="P2" t="n">
-        <v>-14.9846</v>
+        <v>14.3601</v>
       </c>
       <c r="Q2" t="n">
-        <v>-47.2431</v>
+        <v>-23.7255</v>
       </c>
       <c r="R2" t="n">
-        <v>32.2583</v>
+        <v>38.0856</v>
       </c>
       <c r="S2" t="n">
-        <v>28.4104</v>
+        <v>9.3139</v>
       </c>
       <c r="T2" t="n">
-        <v>21.6037</v>
+        <v>3.1859</v>
       </c>
       <c r="U2" t="n">
-        <v>6.8064</v>
+        <v>6.1278</v>
       </c>
       <c r="V2" t="n">
-        <v>-9.198600000000001</v>
+        <v>-6.5277</v>
       </c>
       <c r="W2" t="n">
-        <v>10.6848</v>
+        <v>9.5349</v>
       </c>
       <c r="X2" t="n">
-        <v>-19.8834</v>
+        <v>-16.0623</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>39.657</v>
+        <v>32.241</v>
       </c>
       <c r="E3" t="n">
-        <v>29.6851</v>
+        <v>14.1358</v>
       </c>
       <c r="F3" t="n">
-        <v>9.9719</v>
+        <v>18.1053</v>
       </c>
       <c r="G3" t="n">
-        <v>19.5413</v>
+        <v>4.077</v>
       </c>
       <c r="H3" t="n">
-        <v>18.5591</v>
+        <v>-4.5472</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9820000000000009</v>
+        <v>8.625</v>
       </c>
       <c r="J3" t="n">
-        <v>35.6537</v>
+        <v>27.9962</v>
       </c>
       <c r="K3" t="n">
-        <v>27.9971</v>
+        <v>8.7667</v>
       </c>
       <c r="L3" t="n">
-        <v>7.6561</v>
+        <v>19.2297</v>
       </c>
       <c r="M3" t="n">
-        <v>-16.1123</v>
+        <v>-23.9191</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.438700000000001</v>
+        <v>-13.3143</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.6742</v>
+        <v>-10.6046</v>
       </c>
       <c r="P3" t="n">
-        <v>14.3601</v>
+        <v>29.7607</v>
       </c>
       <c r="Q3" t="n">
-        <v>-23.7255</v>
+        <v>-18.7306</v>
       </c>
       <c r="R3" t="n">
-        <v>38.0856</v>
+        <v>48.4913</v>
       </c>
       <c r="S3" t="n">
-        <v>12.2833</v>
+        <v>-1.1796</v>
       </c>
       <c r="T3" t="n">
-        <v>8.222300000000001</v>
+        <v>-5.0361</v>
       </c>
       <c r="U3" t="n">
-        <v>4.0612</v>
+        <v>3.8563</v>
       </c>
       <c r="V3" t="n">
-        <v>-6.5277</v>
+        <v>-0.4174000000000002</v>
       </c>
       <c r="W3" t="n">
-        <v>9.5349</v>
+        <v>9.9062</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.0623</v>
+        <v>-10.3238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>J. BLACK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>35.4925</v>
+        <v>27.8834</v>
       </c>
       <c r="E4" t="n">
-        <v>9.9598</v>
+        <v>24.5658</v>
       </c>
       <c r="F4" t="n">
-        <v>25.533</v>
+        <v>3.317500000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>11.4269</v>
+        <v>14.7991</v>
       </c>
       <c r="H4" t="n">
-        <v>14.5294</v>
+        <v>1.165899999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.1021</v>
+        <v>13.6333</v>
       </c>
       <c r="J4" t="n">
-        <v>18.9908</v>
+        <v>37.8227</v>
       </c>
       <c r="K4" t="n">
-        <v>16.2311</v>
+        <v>11.2171</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7594</v>
+        <v>26.6055</v>
       </c>
       <c r="M4" t="n">
-        <v>-7.5633</v>
+        <v>-23.024</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7018</v>
+        <v>-10.0514</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.861800000000001</v>
+        <v>-12.9728</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.248600000000001</v>
+        <v>5.6194</v>
       </c>
       <c r="Q4" t="n">
-        <v>-36.6289</v>
+        <v>-36.0045</v>
       </c>
       <c r="R4" t="n">
-        <v>35.3803</v>
+        <v>41.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>22.0412</v>
+        <v>-2.3346</v>
       </c>
       <c r="T4" t="n">
-        <v>10.4034</v>
+        <v>-5.114</v>
       </c>
       <c r="U4" t="n">
-        <v>11.6378</v>
+        <v>2.7789</v>
       </c>
       <c r="V4" t="n">
-        <v>3.2723</v>
+        <v>9.8002</v>
       </c>
       <c r="W4" t="n">
-        <v>17.1946</v>
+        <v>27.8614</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.9221</v>
+        <v>-18.0613</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>20.3903</v>
+        <v>24.9988</v>
       </c>
       <c r="E5" t="n">
-        <v>6.4209</v>
+        <v>12.8266</v>
       </c>
       <c r="F5" t="n">
-        <v>13.9695</v>
+        <v>12.1719</v>
       </c>
       <c r="G5" t="n">
-        <v>4.077</v>
+        <v>37.0134</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.5472</v>
+        <v>31.3374</v>
       </c>
       <c r="I5" t="n">
-        <v>8.625</v>
+        <v>5.676</v>
       </c>
       <c r="J5" t="n">
-        <v>27.9962</v>
+        <v>42.9972</v>
       </c>
       <c r="K5" t="n">
-        <v>8.7667</v>
+        <v>33.2393</v>
       </c>
       <c r="L5" t="n">
-        <v>19.2297</v>
+        <v>9.758000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-23.9191</v>
+        <v>-5.9835</v>
       </c>
       <c r="N5" t="n">
-        <v>-13.3143</v>
+        <v>-1.9018</v>
       </c>
       <c r="O5" t="n">
-        <v>-10.6046</v>
+        <v>-4.082</v>
       </c>
       <c r="P5" t="n">
-        <v>29.7607</v>
+        <v>-14.9846</v>
       </c>
       <c r="Q5" t="n">
-        <v>-18.7306</v>
+        <v>-47.2431</v>
       </c>
       <c r="R5" t="n">
-        <v>48.4913</v>
+        <v>32.2583</v>
       </c>
       <c r="S5" t="n">
-        <v>-13.0303</v>
+        <v>12.1683</v>
       </c>
       <c r="T5" t="n">
-        <v>-12.7513</v>
+        <v>6.387700000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2790999999999999</v>
+        <v>5.7805</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4174000000000002</v>
+        <v>-9.198600000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>9.9062</v>
+        <v>10.6848</v>
       </c>
       <c r="X5" t="n">
-        <v>-10.3238</v>
+        <v>-19.8834</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BLACK</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>14.8219</v>
+        <v>22.383</v>
       </c>
       <c r="E6" t="n">
-        <v>13.7431</v>
+        <v>1.7082</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0784</v>
+        <v>20.6744</v>
       </c>
       <c r="G6" t="n">
-        <v>14.7991</v>
+        <v>11.4269</v>
       </c>
       <c r="H6" t="n">
-        <v>1.165899999999999</v>
+        <v>14.5294</v>
       </c>
       <c r="I6" t="n">
-        <v>13.6333</v>
+        <v>-3.1021</v>
       </c>
       <c r="J6" t="n">
-        <v>37.8227</v>
+        <v>18.9908</v>
       </c>
       <c r="K6" t="n">
-        <v>11.2171</v>
+        <v>16.2311</v>
       </c>
       <c r="L6" t="n">
-        <v>26.6055</v>
+        <v>2.7594</v>
       </c>
       <c r="M6" t="n">
-        <v>-23.024</v>
+        <v>-7.5633</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.0514</v>
+        <v>-1.7018</v>
       </c>
       <c r="O6" t="n">
-        <v>-12.9728</v>
+        <v>-5.861800000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>5.6194</v>
+        <v>-1.248600000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-36.0045</v>
+        <v>-36.6289</v>
       </c>
       <c r="R6" t="n">
-        <v>41.6237</v>
+        <v>35.3803</v>
       </c>
       <c r="S6" t="n">
-        <v>-15.3967</v>
+        <v>8.932</v>
       </c>
       <c r="T6" t="n">
-        <v>-15.9367</v>
+        <v>2.1524</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5401999999999999</v>
+        <v>6.7797</v>
       </c>
       <c r="V6" t="n">
-        <v>9.8002</v>
+        <v>3.2723</v>
       </c>
       <c r="W6" t="n">
-        <v>27.8614</v>
+        <v>17.1946</v>
       </c>
       <c r="X6" t="n">
-        <v>-18.0613</v>
+        <v>-13.9221</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>14.0152</v>
+        <v>11.2318</v>
       </c>
       <c r="E7" t="n">
-        <v>11.9563</v>
+        <v>9.8133</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0589</v>
+        <v>1.4186</v>
       </c>
       <c r="G7" t="n">
         <v>5.389799999999999</v>
@@ -1000,13 +1000,13 @@
         <v>32.2585</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4946</v>
+        <v>0.7113000000000002</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5857</v>
+        <v>-0.5572</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9089</v>
+        <v>1.2687</v>
       </c>
       <c r="V7" t="n">
         <v>6.5879</v>
@@ -1033,13 +1033,13 @@
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>5.607599999999999</v>
+        <v>7.776200000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2787000000000002</v>
+        <v>1.435799999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>5.8863</v>
+        <v>6.340199999999999</v>
       </c>
       <c r="G8" t="n">
         <v>8.535500000000001</v>
@@ -1078,13 +1078,13 @@
         <v>5.8273</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.594</v>
+        <v>-0.4254000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.3024</v>
+        <v>-0.5881000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2915</v>
+        <v>0.1627000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>1.539</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BAENA DELGADO</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1897</v>
+        <v>3.102</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6795000000000001</v>
+        <v>3.698200000000002</v>
       </c>
       <c r="F9" t="n">
-        <v>0.49</v>
+        <v>-0.5956000000000004</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0721</v>
+        <v>21.1301</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1771</v>
+        <v>7.1864</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2493</v>
+        <v>13.9438</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1048</v>
+        <v>39.8467</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0384</v>
+        <v>12.1384</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1431</v>
+        <v>27.7083</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0326</v>
+        <v>-18.7164</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1388</v>
+        <v>-4.952100000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1061</v>
+        <v>-13.7647</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2081</v>
+        <v>-23.1013</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-61.8113</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2081</v>
+        <v>38.7099</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5069</v>
+        <v>0.2615000000000002</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2577</v>
+        <v>-3.4908</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2492</v>
+        <v>3.7517</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1675</v>
+        <v>4.811500000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1675</v>
+        <v>29.1527</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-24.3413</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. SORENSEN</t>
+          <t>J. BAENA DELGADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9528</v>
+        <v>-0.2587</v>
       </c>
       <c r="E10" t="n">
-        <v>-16.6125</v>
+        <v>-0.5724</v>
       </c>
       <c r="F10" t="n">
-        <v>13.6598</v>
+        <v>0.3138</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.593999999999999</v>
+        <v>-2.0721</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8854</v>
+        <v>0.1771</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.708699999999999</v>
+        <v>-2.2493</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.6708</v>
+        <v>-2.1048</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0756</v>
+        <v>0.0384</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.5953</v>
+        <v>-2.1431</v>
       </c>
       <c r="M10" t="n">
-        <v>4.076700000000001</v>
+        <v>0.0326</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8099</v>
+        <v>0.1388</v>
       </c>
       <c r="O10" t="n">
-        <v>5.8865</v>
+        <v>-0.1061</v>
       </c>
       <c r="P10" t="n">
-        <v>3.1219</v>
+        <v>0.2081</v>
       </c>
       <c r="Q10" t="n">
-        <v>-11.4465</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>14.5685</v>
+        <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1577999999999999</v>
+        <v>0.4379</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6037999999999999</v>
+        <v>0.3648</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4460000000000001</v>
+        <v>0.07310000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6381</v>
+        <v>1.1675</v>
       </c>
       <c r="W10" t="n">
-        <v>2.9012</v>
+        <v>1.1675</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.5392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>L. SORENSEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.827399999999999</v>
+        <v>-0.3885999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2311</v>
+        <v>-16.6127</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.596000000000001</v>
+        <v>16.2238</v>
       </c>
       <c r="G11" t="n">
-        <v>21.1301</v>
+        <v>-4.593999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>7.1864</v>
+        <v>-2.8854</v>
       </c>
       <c r="I11" t="n">
-        <v>13.9438</v>
+        <v>-1.708699999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>39.8467</v>
+        <v>-8.6708</v>
       </c>
       <c r="K11" t="n">
-        <v>12.1384</v>
+        <v>-1.0756</v>
       </c>
       <c r="L11" t="n">
-        <v>27.7083</v>
+        <v>-7.5953</v>
       </c>
       <c r="M11" t="n">
-        <v>-18.7164</v>
+        <v>4.076700000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.952100000000001</v>
+        <v>-1.8099</v>
       </c>
       <c r="O11" t="n">
-        <v>-13.7647</v>
+        <v>5.8865</v>
       </c>
       <c r="P11" t="n">
-        <v>-23.1013</v>
+        <v>3.1219</v>
       </c>
       <c r="Q11" t="n">
-        <v>-61.8113</v>
+        <v>-11.4465</v>
       </c>
       <c r="R11" t="n">
-        <v>38.7099</v>
+        <v>14.5685</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.6679</v>
+        <v>2.7218</v>
       </c>
       <c r="T11" t="n">
-        <v>-8.419600000000001</v>
+        <v>0.6038000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7516</v>
+        <v>2.1183</v>
       </c>
       <c r="V11" t="n">
-        <v>4.811500000000001</v>
+        <v>-1.6381</v>
       </c>
       <c r="W11" t="n">
-        <v>29.1527</v>
+        <v>2.9012</v>
       </c>
       <c r="X11" t="n">
-        <v>-24.3413</v>
+        <v>-4.5392</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.177</v>
+        <v>-1.159400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.9601</v>
+        <v>-15.9241</v>
       </c>
       <c r="F12" t="n">
-        <v>9.7829</v>
+        <v>14.7643</v>
       </c>
       <c r="G12" t="n">
         <v>2.805999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>32.0503</v>
       </c>
       <c r="S12" t="n">
-        <v>-11.75</v>
+        <v>-1.7321</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.9743</v>
+        <v>-2.9384</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.7753</v>
+        <v>1.206</v>
       </c>
       <c r="V12" t="n">
         <v>15.2485</v>
@@ -1423,13 +1423,13 @@
         <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.8406</v>
+        <v>-4.733500000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.0803</v>
+        <v>-9.1867</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2394</v>
+        <v>4.4533</v>
       </c>
       <c r="G13" t="n">
         <v>-8.558499999999999</v>
@@ -1468,13 +1468,13 @@
         <v>22.4768</v>
       </c>
       <c r="S13" t="n">
-        <v>-11.8098</v>
+        <v>-2.7024</v>
       </c>
       <c r="T13" t="n">
-        <v>-8.5443</v>
+        <v>-2.6507</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.2655</v>
+        <v>-0.05159999999999994</v>
       </c>
       <c r="V13" t="n">
         <v>-5.3352</v>
@@ -1501,13 +1501,13 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-24.9659</v>
+        <v>-29.7768</v>
       </c>
       <c r="E14" t="n">
-        <v>-23.0564</v>
+        <v>-28.6282</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9095</v>
+        <v>-1.147899999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-16.9267</v>
@@ -1546,13 +1546,13 @@
         <v>28.5122</v>
       </c>
       <c r="S14" t="n">
-        <v>6.3335</v>
+        <v>1.523</v>
       </c>
       <c r="T14" t="n">
-        <v>5.6051</v>
+        <v>0.03329999999999972</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7283000000000002</v>
+        <v>1.4896</v>
       </c>
       <c r="V14" t="n">
         <v>-5.4239</v>
@@ -1579,19 +1579,19 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>114.2719</v>
+        <v>129.9868</v>
       </c>
       <c r="E15" t="n">
-        <v>21.90939999999999</v>
+        <v>21.9086</v>
       </c>
       <c r="F15" t="n">
-        <v>92.3626</v>
+        <v>108.0784</v>
       </c>
       <c r="G15" t="n">
         <v>92.56780000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>60.09490000000001</v>
+        <v>60.0949</v>
       </c>
       <c r="I15" t="n">
         <v>32.4738</v>
@@ -1609,28 +1609,28 @@
         <v>-128.1569</v>
       </c>
       <c r="N15" t="n">
-        <v>-60.1538</v>
+        <v>-60.15379999999999</v>
       </c>
       <c r="O15" t="n">
         <v>-68.00580000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.162700000000003</v>
+        <v>-4.162699999999997</v>
       </c>
       <c r="Q15" t="n">
         <v>-374.6142</v>
       </c>
       <c r="R15" t="n">
-        <v>370.4508</v>
+        <v>370.4508000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>11.97900000000001</v>
+        <v>27.6956</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.646900000000006</v>
+        <v>-7.6474</v>
       </c>
       <c r="U15" t="n">
-        <v>19.6262</v>
+        <v>35.34170000000001</v>
       </c>
       <c r="V15" t="n">
         <v>13.886</v>
